--- a/Performance_Projetos.xlsx
+++ b/Performance_Projetos.xlsx
@@ -1447,7 +1447,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Z2"/>
+  <dimension ref="A1:Z3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="14.5"/>
   <cols>
     <col width="8.7265625" customWidth="1" style="1" min="1" max="1"/>
@@ -1679,7 +1679,78 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>Em análise</t>
+          <t>Validação</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="n">
+        <v>2</v>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>Um banco único que irá conter todos os dados em relação à infiltração.</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>2026-07-21 13:00:37.003037</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>Guilherme de Oliveira Ferreira</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>90014149</t>
+        </is>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>Berbara Raposo</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>Performance</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>Banco de dados do Water Leak desalinhados uns com os outros.</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>Sistema interno, interferindo time do RTC pintura.</t>
+        </is>
+      </c>
+      <c r="O3" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="P3" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="Q3" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="V3" t="n">
+        <v>0</v>
+      </c>
+      <c r="W3" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y3" t="inlineStr">
+        <is>
+          <t>Validação</t>
         </is>
       </c>
     </row>

--- a/Performance_Projetos.xlsx
+++ b/Performance_Projetos.xlsx
@@ -1656,6 +1656,29 @@
           <t>no próprio celular ou computador de cada um!</t>
         </is>
       </c>
+      <c r="J2" t="n">
+        <v>0</v>
+      </c>
+      <c r="K2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="L2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="M2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="N2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
       <c r="O2" t="inlineStr">
         <is>
           <t>0</t>
@@ -1667,6 +1690,26 @@
         </is>
       </c>
       <c r="Q2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="R2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="S2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="T2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="U2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
@@ -1677,9 +1720,12 @@
       <c r="W2" t="n">
         <v>0</v>
       </c>
+      <c r="X2" t="n">
+        <v>1</v>
+      </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>Validação</t>
+          <t>Implementação</t>
         </is>
       </c>
     </row>
@@ -1727,6 +1773,29 @@
           <t>Sistema interno, interferindo time do RTC pintura.</t>
         </is>
       </c>
+      <c r="J3" t="n">
+        <v>0</v>
+      </c>
+      <c r="K3" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="L3" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="M3" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="N3" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
       <c r="O3" t="inlineStr">
         <is>
           <t>0</t>
@@ -1738,6 +1807,26 @@
         </is>
       </c>
       <c r="Q3" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="R3" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="S3" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="T3" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="U3" t="inlineStr">
         <is>
           <t>0</t>
         </is>
@@ -1748,9 +1837,12 @@
       <c r="W3" t="n">
         <v>0</v>
       </c>
+      <c r="X3" t="n">
+        <v>1</v>
+      </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>Validação</t>
+          <t>Execução Rápida</t>
         </is>
       </c>
     </row>

--- a/Performance_Projetos.xlsx
+++ b/Performance_Projetos.xlsx
@@ -1447,7 +1447,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Z3"/>
+  <dimension ref="A1:Z4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="14.5"/>
   <cols>
     <col width="8.7265625" customWidth="1" style="1" min="1" max="1"/>
@@ -1657,62 +1657,40 @@
         </is>
       </c>
       <c r="J2" t="n">
+        <v>700</v>
+      </c>
+      <c r="K2" t="n">
         <v>0</v>
       </c>
-      <c r="K2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="L2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="M2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="N2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="O2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="P2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="Q2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="R2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="S2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="T2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="U2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
+      <c r="L2" t="n">
+        <v>0</v>
+      </c>
+      <c r="M2" t="n">
+        <v>0</v>
+      </c>
+      <c r="N2" t="n">
+        <v>0</v>
+      </c>
+      <c r="O2" t="n">
+        <v>0</v>
+      </c>
+      <c r="P2" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q2" t="n">
+        <v>0</v>
+      </c>
+      <c r="R2" t="n">
+        <v>9</v>
+      </c>
+      <c r="S2" t="n">
+        <v>0</v>
+      </c>
+      <c r="T2" t="n">
+        <v>0</v>
+      </c>
+      <c r="U2" t="n">
+        <v>0</v>
       </c>
       <c r="V2" t="n">
         <v>0</v>
@@ -1774,61 +1752,61 @@
         </is>
       </c>
       <c r="J3" t="n">
-        <v>0</v>
+        <v>1500</v>
       </c>
       <c r="K3" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>6</t>
         </is>
       </c>
       <c r="L3" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>3</t>
         </is>
       </c>
       <c r="M3" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>9</t>
         </is>
       </c>
       <c r="N3" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>6</t>
         </is>
       </c>
       <c r="O3" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>3</t>
         </is>
       </c>
       <c r="P3" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>3</t>
         </is>
       </c>
       <c r="Q3" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>3</t>
         </is>
       </c>
       <c r="R3" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>9</t>
         </is>
       </c>
       <c r="S3" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>9</t>
         </is>
       </c>
       <c r="T3" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>6</t>
         </is>
       </c>
       <c r="U3" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>3</t>
         </is>
       </c>
       <c r="V3" t="n">
@@ -1838,11 +1816,128 @@
         <v>0</v>
       </c>
       <c r="X3" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="Y3" t="inlineStr">
         <is>
           <t>Execução Rápida</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="n">
+        <v>3</v>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>Placas de Aviso para uso de EPI's</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>2026-07-21 16:44:20.947746</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>Guilherme de Oliveira Ferreira</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>90014149</t>
+        </is>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>Berbara Raposo</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>Performance</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>Falta de Avisos de Segurança nas Linhas.</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>Paint &amp; Plastic Shop</t>
+        </is>
+      </c>
+      <c r="J4" t="n">
+        <v>300</v>
+      </c>
+      <c r="K4" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="L4" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="M4" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="N4" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="O4" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="P4" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="Q4" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="R4" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="S4" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="T4" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="U4" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="V4" t="n">
+        <v>0</v>
+      </c>
+      <c r="W4" t="n">
+        <v>0</v>
+      </c>
+      <c r="X4" t="n">
+        <v>3</v>
+      </c>
+      <c r="Y4" t="inlineStr">
+        <is>
+          <t>Incubadora</t>
         </is>
       </c>
     </row>
